--- a/data/trans_dic/IP31KM06_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM06_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,9; 39,53</t>
+          <t>24,61; 39,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,24; 42,29</t>
+          <t>25,5; 40,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,29; 37,98</t>
+          <t>27,53; 37,89</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>45,44%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,95; 40,0</t>
+          <t>36,07; 54,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,43; 53,63</t>
+          <t>24,09; 40,34</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,45; 44,17</t>
+          <t>32,48; 44,1</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>33,44%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>19,93; 40,34</t>
+          <t>26,08; 48,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>23,83; 47,41</t>
+          <t>19,5; 42,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,92; 39,52</t>
+          <t>25,73; 42,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,63; 61,27</t>
+          <t>31,16; 45,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,7; 44,36</t>
+          <t>28,86; 41,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,44; 50,82</t>
+          <t>31,87; 41,21</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>40,17%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>31,88; 48,42</t>
+          <t>32,34; 52,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>31,29; 53,18</t>
+          <t>32,64; 47,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33,82; 48,39</t>
+          <t>34,54; 47,57</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>34,8%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20,74; 39,78</t>
+          <t>26,18; 48,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>27,61; 48,65</t>
+          <t>23,12; 44,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,03; 41,23</t>
+          <t>28,14; 43,0</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,35%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31,49; 46,15</t>
+          <t>34,74; 42,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>34,49; 42,27</t>
+          <t>30,97; 37,74</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33,77; 41,22</t>
+          <t>34,0; 38,87</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>47</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32105</t>
+          <t>38991</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43656</t>
+          <t>33177</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75762</t>
+          <t>72168</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>24310; 40202</t>
+          <t>29828; 48157</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34119; 57167</t>
+          <t>25586; 40962</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62287; 89971</t>
+          <t>61003; 83938</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>40</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>29306</t>
+          <t>40841</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>42027</t>
+          <t>29969</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71334</t>
+          <t>70810</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22365; 37358</t>
+          <t>32417; 48538</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33204; 50257</t>
+          <t>22989; 38489</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60713; 82636</t>
+          <t>60174; 81718</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14698</t>
+          <t>20518</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21664</t>
+          <t>15551</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36362</t>
+          <t>36070</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9981; 20205</t>
+          <t>14562; 26954</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>14857; 29550</t>
+          <t>10140; 22218</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26896; 44430</t>
+          <t>27755; 45328</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>84562</t>
+          <t>74849</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80623</t>
+          <t>61203</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165186</t>
+          <t>136051</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61711; 132067</t>
+          <t>61482; 89654</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65287; 94332</t>
+          <t>50980; 73626</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>138897; 217596</t>
+          <t>119176; 154120</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46017</t>
+          <t>58909</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63666</t>
+          <t>45962</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>109683</t>
+          <t>104870</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36829; 55931</t>
+          <t>47083; 76954</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>49899; 84797</t>
+          <t>37683; 55291</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92994; 133070</t>
+          <t>90169; 124180</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>30</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>21013</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25935</t>
+          <t>22760</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46947</t>
+          <t>47411</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>14290; 27405</t>
+          <t>17242; 32014</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19060; 33585</t>
+          <t>16265; 31162</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35897; 56871</t>
+          <t>38333; 58576</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>287</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>227702</t>
+          <t>258759</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>277571</t>
+          <t>208622</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>505273</t>
+          <t>467381</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>203170; 297728</t>
+          <t>234735; 286006</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>252558; 309597</t>
+          <t>188970; 230310</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>465170; 567817</t>
+          <t>437239; 499894</t>
         </is>
       </c>
     </row>
